--- a/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_cw.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_bulgaria/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F471B6B9-6A58-A54D-8FC5-4229FE305C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A86A069-7186-5A4C-9DB0-C7945D95899A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7140" windowWidth="25600" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="-7140" windowWidth="51200" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1474,7 +1474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1567,9 +1567,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1918,31 +1915,31 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="13.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="62.5" style="4" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="33.1640625" style="4" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="47.5" style="4" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="48.5" style="4" hidden="1" customWidth="1"/>
     <col min="9" max="10" width="35" style="4" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="31.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.83203125" style="38" customWidth="1"/>
-    <col min="13" max="15" width="20.5" style="40" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5" style="41" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5" style="43" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.5" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" style="37" customWidth="1"/>
+    <col min="13" max="15" width="20.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" style="41" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
@@ -2018,14 +2015,10 @@
       <c r="L2" s="13">
         <v>12</v>
       </c>
-      <c r="M2" s="16">
-        <v>1</v>
-      </c>
-      <c r="N2" s="16">
-        <v>1</v>
-      </c>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
       <c r="O2" s="16">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
@@ -2036,7 +2029,7 @@
       <c r="A3" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="44" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="17" t="s">
@@ -2064,7 +2057,7 @@
       <c r="M3" s="16"/>
       <c r="N3" s="16"/>
       <c r="O3" s="16">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
@@ -2103,7 +2096,7 @@
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
       <c r="O4" s="16">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -2139,15 +2132,9 @@
       <c r="L5" s="13">
         <v>12</v>
       </c>
-      <c r="M5" s="16">
-        <v>1</v>
-      </c>
-      <c r="N5" s="16">
-        <v>1</v>
-      </c>
-      <c r="O5" s="16">
-        <v>1</v>
-      </c>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="11"/>
@@ -2188,9 +2175,7 @@
       </c>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
-      <c r="O6" s="16">
-        <v>0.1</v>
-      </c>
+      <c r="O6" s="16"/>
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="11"/>
@@ -2226,10 +2211,10 @@
         <v>12</v>
       </c>
       <c r="M7" s="16"/>
-      <c r="N7" s="46">
+      <c r="N7" s="45">
         <v>0.05</v>
       </c>
-      <c r="O7" s="46">
+      <c r="O7" s="45">
         <v>0.1</v>
       </c>
       <c r="P7" s="10"/>
@@ -2270,9 +2255,11 @@
       <c r="L8" s="13">
         <v>12</v>
       </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="46">
-        <v>1</v>
+      <c r="M8" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N8" s="45">
+        <v>0.5</v>
       </c>
       <c r="O8" s="16">
         <v>1</v>
@@ -2316,9 +2303,7 @@
         <v>12</v>
       </c>
       <c r="M9" s="16"/>
-      <c r="N9" s="46">
-        <v>1</v>
-      </c>
+      <c r="N9" s="45"/>
       <c r="O9" s="16">
         <v>1</v>
       </c>
@@ -2360,9 +2345,11 @@
       <c r="L10" s="13">
         <v>12</v>
       </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="46">
-        <v>1</v>
+      <c r="M10" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N10" s="45">
+        <v>0.5</v>
       </c>
       <c r="O10" s="16">
         <v>1</v>
@@ -2401,9 +2388,11 @@
       <c r="L11" s="13">
         <v>12</v>
       </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="46">
-        <v>1</v>
+      <c r="M11" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N11" s="45">
+        <v>0.5</v>
       </c>
       <c r="O11" s="16">
         <v>1</v>
@@ -2442,9 +2431,11 @@
       <c r="L12" s="13">
         <v>12</v>
       </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="46">
-        <v>1</v>
+      <c r="M12" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N12" s="45">
+        <v>0.5</v>
       </c>
       <c r="O12" s="16">
         <v>1</v>
@@ -2488,10 +2479,10 @@
         <v>12</v>
       </c>
       <c r="M13" s="16">
-        <v>1</v>
-      </c>
-      <c r="N13" s="46">
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="N13" s="45">
+        <v>0.5</v>
       </c>
       <c r="O13" s="16">
         <v>1</v>
@@ -2534,9 +2525,11 @@
       <c r="L14" s="13">
         <v>12</v>
       </c>
-      <c r="M14" s="16"/>
-      <c r="N14" s="46">
-        <v>1</v>
+      <c r="M14" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N14" s="45">
+        <v>0.5</v>
       </c>
       <c r="O14" s="16">
         <v>1</v>
@@ -2576,9 +2569,7 @@
         <v>12</v>
       </c>
       <c r="M15" s="16"/>
-      <c r="N15" s="46">
-        <v>1</v>
-      </c>
+      <c r="N15" s="45"/>
       <c r="O15" s="16">
         <v>1</v>
       </c>
@@ -2621,7 +2612,9 @@
         <v>12</v>
       </c>
       <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
+      <c r="N16" s="16">
+        <v>1</v>
+      </c>
       <c r="O16" s="16">
         <v>1</v>
       </c>
@@ -2630,7 +2623,7 @@
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
     </row>
-    <row r="17" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>51</v>
       </c>
@@ -2673,7 +2666,7 @@
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
     </row>
-    <row r="18" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2716,7 +2709,7 @@
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
     </row>
-    <row r="19" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2746,7 +2739,9 @@
         <v>12</v>
       </c>
       <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
+      <c r="N19" s="16">
+        <v>1</v>
+      </c>
       <c r="O19" s="16">
         <v>1</v>
       </c>
@@ -2755,7 +2750,7 @@
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
     </row>
-    <row r="20" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -2794,7 +2789,7 @@
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
     </row>
-    <row r="21" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -2802,7 +2797,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>68</v>
@@ -2833,7 +2828,7 @@
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
     </row>
-    <row r="22" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>210</v>
       </c>
@@ -2867,7 +2862,7 @@
         <v>12</v>
       </c>
       <c r="M22" s="16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N22" s="16">
         <v>1</v>
@@ -2880,7 +2875,7 @@
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
     </row>
-    <row r="23" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>210</v>
       </c>
@@ -2921,7 +2916,7 @@
       <c r="R23" s="11"/>
       <c r="S23" s="11"/>
     </row>
-    <row r="24" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>210</v>
       </c>
@@ -2955,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="M24" s="16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N24" s="16">
         <v>1</v>
@@ -2968,7 +2963,7 @@
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
     </row>
-    <row r="25" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>210</v>
       </c>
@@ -3009,7 +3004,7 @@
       <c r="R25" s="11"/>
       <c r="S25" s="11"/>
     </row>
-    <row r="26" spans="1:19" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>210</v>
       </c>
@@ -3040,15 +3035,13 @@
       </c>
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
-      <c r="O26" s="16">
-        <v>1</v>
-      </c>
+      <c r="O26" s="16"/>
       <c r="P26" s="28"/>
       <c r="Q26" s="28"/>
       <c r="R26" s="29"/>
       <c r="S26" s="30"/>
     </row>
-    <row r="27" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>210</v>
       </c>
@@ -3079,15 +3072,13 @@
       </c>
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
-      <c r="O27" s="16">
-        <v>1</v>
-      </c>
+      <c r="O27" s="16"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="11"/>
       <c r="S27" s="11"/>
     </row>
-    <row r="28" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>210</v>
       </c>
@@ -3118,15 +3109,13 @@
       </c>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
-      <c r="O28" s="16">
-        <v>1</v>
-      </c>
+      <c r="O28" s="16"/>
       <c r="P28" s="10"/>
       <c r="Q28" s="10"/>
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
     </row>
-    <row r="29" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>210</v>
       </c>
@@ -3157,15 +3146,13 @@
       </c>
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
-      <c r="O29" s="16">
-        <v>1</v>
-      </c>
+      <c r="O29" s="16"/>
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="11"/>
       <c r="S29" s="11"/>
     </row>
-    <row r="30" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>210</v>
       </c>
@@ -3196,15 +3183,13 @@
       </c>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
-      <c r="O30" s="16">
-        <v>1</v>
-      </c>
+      <c r="O30" s="16"/>
       <c r="P30" s="10"/>
       <c r="Q30" s="10"/>
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
     </row>
-    <row r="31" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>210</v>
       </c>
@@ -3235,15 +3220,13 @@
       </c>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
-      <c r="O31" s="16">
-        <v>1</v>
-      </c>
+      <c r="O31" s="16"/>
       <c r="P31" s="10"/>
       <c r="Q31" s="10"/>
       <c r="R31" s="11"/>
       <c r="S31" s="11"/>
     </row>
-    <row r="32" spans="1:19" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>210</v>
       </c>
@@ -3278,13 +3261,13 @@
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
-      <c r="O32" s="16">
-        <v>0.1</v>
-      </c>
+      <c r="O32" s="16"/>
       <c r="P32" s="31"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="32"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
     </row>
     <row r="33" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
@@ -3315,9 +3298,15 @@
       <c r="L33" s="13">
         <v>12</v>
       </c>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
+      <c r="M33" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N33" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="O33" s="16">
+        <v>1</v>
+      </c>
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
       <c r="R33" s="11"/>
@@ -3354,9 +3343,7 @@
       </c>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
-      <c r="O34" s="16">
-        <v>1</v>
-      </c>
+      <c r="O34" s="16"/>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="11"/>
@@ -3391,9 +3378,11 @@
       <c r="L35" s="13">
         <v>12</v>
       </c>
-      <c r="M35" s="16"/>
-      <c r="N35" s="46">
-        <v>1</v>
+      <c r="M35" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N35" s="45">
+        <v>0.5</v>
       </c>
       <c r="O35" s="16">
         <v>1</v>
@@ -3432,15 +3421,9 @@
       <c r="L36" s="13">
         <v>12</v>
       </c>
-      <c r="M36" s="16">
-        <v>1</v>
-      </c>
-      <c r="N36" s="46">
-        <v>1</v>
-      </c>
-      <c r="O36" s="16">
-        <v>1</v>
-      </c>
+      <c r="M36" s="16"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="16"/>
       <c r="P36" s="10"/>
       <c r="Q36" s="10"/>
       <c r="R36" s="11"/>
@@ -3476,12 +3459,8 @@
         <v>12</v>
       </c>
       <c r="M37" s="16"/>
-      <c r="N37" s="46">
-        <v>1</v>
-      </c>
-      <c r="O37" s="16">
-        <v>1</v>
-      </c>
+      <c r="N37" s="45"/>
+      <c r="O37" s="16"/>
       <c r="P37" s="10"/>
       <c r="Q37" s="10"/>
       <c r="R37" s="11"/>
@@ -3517,12 +3496,8 @@
         <v>12</v>
       </c>
       <c r="M38" s="16"/>
-      <c r="N38" s="16">
-        <v>1</v>
-      </c>
-      <c r="O38" s="16">
-        <v>1</v>
-      </c>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
       <c r="P38" s="10"/>
       <c r="Q38" s="10"/>
       <c r="R38" s="11"/>
@@ -3557,15 +3532,9 @@
       <c r="L39" s="13">
         <v>12</v>
       </c>
-      <c r="M39" s="16">
-        <v>1</v>
-      </c>
-      <c r="N39" s="16">
-        <v>1</v>
-      </c>
-      <c r="O39" s="16">
-        <v>1</v>
-      </c>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
       <c r="P39" s="10"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="11"/>
@@ -3605,13 +3574,13 @@
         <v>12</v>
       </c>
       <c r="M40" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N40" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="O40" s="16">
         <v>1</v>
-      </c>
-      <c r="N40" s="46">
-        <v>1</v>
-      </c>
-      <c r="O40" s="16">
-        <v>2</v>
       </c>
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
@@ -3638,7 +3607,7 @@
         <v>327</v>
       </c>
       <c r="G41" s="12"/>
-      <c r="H41" s="33"/>
+      <c r="H41" s="32"/>
       <c r="I41" s="12" t="s">
         <v>328</v>
       </c>
@@ -3652,7 +3621,7 @@
         <v>12</v>
       </c>
       <c r="M41" s="16"/>
-      <c r="N41" s="46">
+      <c r="N41" s="45">
         <v>1</v>
       </c>
       <c r="O41" s="16">
@@ -3683,7 +3652,7 @@
         <v>331</v>
       </c>
       <c r="G42" s="12"/>
-      <c r="H42" s="33"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="12" t="s">
         <v>332</v>
       </c>
@@ -3697,7 +3666,7 @@
         <v>12</v>
       </c>
       <c r="M42" s="16"/>
-      <c r="N42" s="46">
+      <c r="N42" s="45">
         <v>1</v>
       </c>
       <c r="O42" s="16">
@@ -3738,7 +3707,7 @@
         <v>12</v>
       </c>
       <c r="M43" s="16"/>
-      <c r="N43" s="46">
+      <c r="N43" s="45">
         <v>1</v>
       </c>
       <c r="O43" s="16">
@@ -3779,9 +3748,9 @@
         <v>12</v>
       </c>
       <c r="M44" s="16">
-        <v>1</v>
-      </c>
-      <c r="N44" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="N44" s="45">
         <v>1</v>
       </c>
       <c r="O44" s="16">
@@ -3826,7 +3795,7 @@
         <v>12</v>
       </c>
       <c r="M45" s="16"/>
-      <c r="N45" s="46">
+      <c r="N45" s="45">
         <v>1</v>
       </c>
       <c r="O45" s="16">
@@ -3871,9 +3840,9 @@
         <v>12</v>
       </c>
       <c r="M46" s="16">
-        <v>1</v>
-      </c>
-      <c r="N46" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="N46" s="45">
         <v>1</v>
       </c>
       <c r="O46" s="16">
@@ -3914,13 +3883,13 @@
         <v>12</v>
       </c>
       <c r="M47" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="N47" s="45">
         <v>1</v>
       </c>
-      <c r="N47" s="46">
+      <c r="O47" s="16">
         <v>1</v>
-      </c>
-      <c r="O47" s="16">
-        <v>2</v>
       </c>
       <c r="P47" s="10"/>
       <c r="Q47" s="10"/>
@@ -3963,18 +3932,18 @@
       <c r="M48" s="16">
         <v>1</v>
       </c>
-      <c r="N48" s="46">
+      <c r="N48" s="45">
         <v>1</v>
       </c>
       <c r="O48" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" s="10"/>
       <c r="Q48" s="10"/>
       <c r="R48" s="11"/>
       <c r="S48" s="11"/>
     </row>
-    <row r="49" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>224</v>
       </c>
@@ -4010,18 +3979,18 @@
       <c r="M49" s="16">
         <v>1</v>
       </c>
-      <c r="N49" s="46">
+      <c r="N49" s="45">
         <v>1</v>
       </c>
       <c r="O49" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P49" s="10"/>
       <c r="Q49" s="10"/>
       <c r="R49" s="11"/>
       <c r="S49" s="11"/>
     </row>
-    <row r="50" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>224</v>
       </c>
@@ -4055,9 +4024,7 @@
         <v>12</v>
       </c>
       <c r="M50" s="16"/>
-      <c r="N50" s="46">
-        <v>1</v>
-      </c>
+      <c r="N50" s="45"/>
       <c r="O50" s="16">
         <v>1</v>
       </c>
@@ -4066,7 +4033,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="11"/>
     </row>
-    <row r="51" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>51</v>
       </c>
@@ -4095,8 +4062,12 @@
       <c r="L51" s="13">
         <v>12</v>
       </c>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
+      <c r="M51" s="16">
+        <v>1</v>
+      </c>
+      <c r="N51" s="16">
+        <v>1</v>
+      </c>
       <c r="O51" s="16">
         <v>1</v>
       </c>
@@ -4105,7 +4076,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="11"/>
     </row>
-    <row r="52" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>51</v>
       </c>
@@ -4140,15 +4111,13 @@
       </c>
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
-      <c r="O52" s="16">
-        <v>1</v>
-      </c>
+      <c r="O52" s="16"/>
       <c r="P52" s="10"/>
       <c r="Q52" s="10"/>
       <c r="R52" s="11"/>
       <c r="S52" s="11"/>
     </row>
-    <row r="53" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>367</v>
       </c>
@@ -4181,17 +4150,21 @@
       <c r="L53" s="13">
         <v>12</v>
       </c>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
+      <c r="M53" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N53" s="16">
+        <v>0.5</v>
+      </c>
       <c r="O53" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P53" s="10"/>
       <c r="Q53" s="10"/>
       <c r="R53" s="11"/>
       <c r="S53" s="11"/>
     </row>
-    <row r="54" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>367</v>
       </c>
@@ -4224,8 +4197,12 @@
       <c r="L54" s="13">
         <v>12</v>
       </c>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
+      <c r="M54" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N54" s="16">
+        <v>0.5</v>
+      </c>
       <c r="O54" s="16">
         <v>1</v>
       </c>
@@ -4234,7 +4211,7 @@
       <c r="R54" s="11"/>
       <c r="S54" s="11"/>
     </row>
-    <row r="55" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>367</v>
       </c>
@@ -4267,8 +4244,12 @@
       <c r="L55" s="13">
         <v>12</v>
       </c>
-      <c r="M55" s="16"/>
-      <c r="N55" s="16"/>
+      <c r="M55" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="N55" s="16">
+        <v>0.5</v>
+      </c>
       <c r="O55" s="16">
         <v>1</v>
       </c>
@@ -4277,7 +4258,7 @@
       <c r="R55" s="11"/>
       <c r="S55" s="11"/>
     </row>
-    <row r="56" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>367</v>
       </c>
@@ -4312,15 +4293,13 @@
       </c>
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
-      <c r="O56" s="16">
-        <v>1</v>
-      </c>
+      <c r="O56" s="16"/>
       <c r="P56" s="10"/>
       <c r="Q56" s="10"/>
       <c r="R56" s="11"/>
       <c r="S56" s="11"/>
     </row>
-    <row r="57" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>367</v>
       </c>
@@ -4351,15 +4330,13 @@
       </c>
       <c r="M57" s="16"/>
       <c r="N57" s="16"/>
-      <c r="O57" s="16">
-        <v>1</v>
-      </c>
+      <c r="O57" s="16"/>
       <c r="P57" s="10"/>
       <c r="Q57" s="10"/>
       <c r="R57" s="11"/>
       <c r="S57" s="11"/>
     </row>
-    <row r="58" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>367</v>
       </c>
@@ -4394,15 +4371,13 @@
       </c>
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
-      <c r="O58" s="16">
-        <v>1</v>
-      </c>
+      <c r="O58" s="16"/>
       <c r="P58" s="10"/>
       <c r="Q58" s="10"/>
       <c r="R58" s="11"/>
       <c r="S58" s="11"/>
     </row>
-    <row r="59" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>367</v>
       </c>
@@ -4433,15 +4408,15 @@
       </c>
       <c r="M59" s="16"/>
       <c r="N59" s="16"/>
-      <c r="O59" s="16">
-        <v>1</v>
-      </c>
+      <c r="O59" s="16"/>
       <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="11"/>
-      <c r="S59" s="11"/>
-    </row>
-    <row r="60" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q59" s="31"/>
+      <c r="R59" s="29"/>
+      <c r="S59" s="30"/>
+      <c r="T59"/>
+      <c r="U59"/>
+    </row>
+    <row r="60" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>367</v>
       </c>
@@ -4472,15 +4447,15 @@
       </c>
       <c r="M60" s="16"/>
       <c r="N60" s="16"/>
-      <c r="O60" s="16">
-        <v>1</v>
-      </c>
+      <c r="O60" s="16"/>
       <c r="P60" s="10"/>
-      <c r="Q60" s="10"/>
-      <c r="R60" s="11"/>
-      <c r="S60" s="11"/>
-    </row>
-    <row r="61" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q60" s="31"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="30"/>
+      <c r="T60"/>
+      <c r="U60"/>
+    </row>
+    <row r="61" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>367</v>
       </c>
@@ -4507,7 +4482,7 @@
       <c r="J61" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="K61" s="34">
+      <c r="K61" s="33">
         <v>1</v>
       </c>
       <c r="L61" s="13">
@@ -4515,15 +4490,15 @@
       </c>
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
-      <c r="O61" s="16">
-        <v>1</v>
-      </c>
+      <c r="O61" s="16"/>
       <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="11"/>
-      <c r="S61" s="11"/>
-    </row>
-    <row r="62" spans="1:19" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q61" s="31"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="28"/>
+      <c r="T61"/>
+      <c r="U61"/>
+    </row>
+    <row r="62" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>367</v>
       </c>
@@ -4557,20 +4532,22 @@
         <v>12</v>
       </c>
       <c r="M62" s="16">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="N62" s="16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O62" s="16">
         <v>1</v>
       </c>
       <c r="P62" s="10"/>
-      <c r="Q62" s="10"/>
-      <c r="R62" s="11"/>
-      <c r="S62" s="11"/>
-    </row>
-    <row r="63" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q62" s="41"/>
+      <c r="R62" s="39"/>
+      <c r="S62" s="42"/>
+      <c r="T62"/>
+      <c r="U62"/>
+    </row>
+    <row r="63" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="19"/>
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
@@ -4581,17 +4558,14 @@
       <c r="H63" s="19"/>
       <c r="I63" s="19"/>
       <c r="J63" s="19"/>
-      <c r="K63" s="36"/>
-      <c r="L63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="34"/>
       <c r="M63" s="29"/>
       <c r="N63" s="29"/>
       <c r="O63" s="29"/>
       <c r="P63" s="31"/>
-      <c r="Q63" s="31"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="30"/>
-    </row>
-    <row r="64" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="19"/>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -4602,17 +4576,14 @@
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
       <c r="J64" s="19"/>
-      <c r="K64" s="36"/>
-      <c r="L64" s="35"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="34"/>
       <c r="M64" s="29"/>
       <c r="N64" s="29"/>
       <c r="O64" s="29"/>
       <c r="P64" s="31"/>
-      <c r="Q64" s="31"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="30"/>
-    </row>
-    <row r="65" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="19"/>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
@@ -4623,32 +4594,17 @@
       <c r="H65" s="19"/>
       <c r="I65" s="19"/>
       <c r="J65" s="19"/>
-      <c r="K65" s="36"/>
-      <c r="L65" s="35"/>
+      <c r="K65" s="35"/>
+      <c r="L65" s="34"/>
       <c r="M65" s="29"/>
       <c r="N65" s="29"/>
       <c r="O65" s="29"/>
-      <c r="P65" s="37"/>
-      <c r="Q65" s="31"/>
-      <c r="R65" s="29"/>
-      <c r="S65" s="28"/>
+      <c r="P65" s="36"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="M1:O39 M40:N40 M41:O1048576">
+  <conditionalFormatting sqref="M1:O1048576">
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O40">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
